--- a/projects/r-accessible-tables/demo_mikrozensus_accessible_fixed.xlsx
+++ b/projects/r-accessible-tables/demo_mikrozensus_accessible_fixed.xlsx
@@ -25,6 +25,9 @@
     <t xml:space="preserve">demographie</t>
   </si>
   <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
     <t xml:space="preserve">erwerbstätigkeit</t>
   </si>
   <si>
@@ -40,9 +43,6 @@
     <t xml:space="preserve">familie</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
     <t xml:space="preserve">personen id</t>
   </si>
   <si>
@@ -271,7 +271,7 @@
     <t xml:space="preserve">Created</t>
   </si>
   <si>
-    <t xml:space="preserve">2025-11-20 14:23</t>
+    <t xml:space="preserve">2025-11-20 14:26</t>
   </si>
   <si>
     <t xml:space="preserve">Format</t>
@@ -285,7 +285,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -300,13 +300,24 @@
       <b/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <b/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -315,12 +326,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
+        <fgColor rgb="FF366092"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E2F3"/>
+        <fgColor rgb="FF4F81BD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7D4F0"/>
       </patternFill>
     </fill>
     <fill>
@@ -329,7 +345,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -337,19 +353,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -644,8 +694,8 @@
     <col min="2" max="2" width="17.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="20.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="19.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="18.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="17.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20.74875" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="21.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="18.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="17.71" hidden="0" customWidth="1"/>
@@ -660,7 +710,7 @@
     <col min="18" max="18" width="26.71" hidden="0" customWidth="1"/>
     <col min="19" max="19" width="20.71" hidden="0" customWidth="1"/>
     <col min="20" max="20" width="19.71" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="18.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="16.145" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -698,16 +748,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>3</v>
@@ -719,504 +769,510 @@
         <v>3</v>
       </c>
       <c r="I5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="U6" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>85.4</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>850</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="R8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>450</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>92.1</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>890</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>650</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>950</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="S11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="U11" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>69.1</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>89.6</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>1100</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="S12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>380</v>
+      </c>
+      <c r="U12" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>780</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="O13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q13" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="U6" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="C7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="E7" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="G7" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="H7" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" t="n">
-        <v>85.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>850</v>
-      </c>
-      <c r="K7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L7" t="s">
-        <v>33</v>
-      </c>
-      <c r="M7" t="s">
-        <v>34</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2</v>
-      </c>
-      <c r="O7" t="s">
-        <v>32</v>
-      </c>
-      <c r="P7" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="s">
-        <v>34</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>450</v>
-      </c>
-      <c r="U7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="D8" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="E8" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H8" t="s">
-        <v>38</v>
-      </c>
-      <c r="I8" t="n">
-        <v>92.1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1200</v>
-      </c>
-      <c r="K8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M8" t="s">
-        <v>32</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="s">
-        <v>34</v>
-      </c>
-      <c r="P8" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>12</v>
-      </c>
-      <c r="R8" t="s">
-        <v>34</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>890</v>
-      </c>
-      <c r="U8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" t="n">
-        <v>52.7</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E9" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="H9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I9" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>650</v>
-      </c>
-      <c r="K9" t="s">
-        <v>32</v>
-      </c>
-      <c r="L9" t="s">
-        <v>33</v>
-      </c>
-      <c r="M9" t="s">
-        <v>34</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3</v>
-      </c>
-      <c r="O9" t="s">
-        <v>32</v>
-      </c>
-      <c r="P9" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="s">
-        <v>32</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="R13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="S13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D10" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="E10" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="F10" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H10" t="s">
-        <v>46</v>
-      </c>
-      <c r="I10" t="n">
-        <v>105.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>950</v>
-      </c>
-      <c r="K10" t="s">
-        <v>34</v>
-      </c>
-      <c r="L10" t="s">
-        <v>47</v>
-      </c>
-      <c r="M10" t="s">
-        <v>32</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="s">
-        <v>32</v>
-      </c>
-      <c r="P10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>8</v>
-      </c>
-      <c r="R10" t="s">
-        <v>34</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1200</v>
-      </c>
-      <c r="U10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" t="n">
-        <v>67.8</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="E11" t="n">
-        <v>69.1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="G11" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="H11" t="s">
-        <v>50</v>
-      </c>
-      <c r="I11" t="n">
-        <v>89.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1100</v>
-      </c>
-      <c r="K11" t="s">
-        <v>34</v>
-      </c>
-      <c r="L11" t="s">
-        <v>33</v>
-      </c>
-      <c r="M11" t="s">
-        <v>32</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O11" t="s">
-        <v>34</v>
-      </c>
-      <c r="P11" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>6</v>
-      </c>
-      <c r="R11" t="s">
-        <v>32</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>380</v>
-      </c>
-      <c r="U11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="D12" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="F12" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="H12" t="s">
-        <v>53</v>
-      </c>
-      <c r="I12" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>780</v>
-      </c>
-      <c r="K12" t="s">
-        <v>32</v>
-      </c>
-      <c r="L12" t="s">
-        <v>39</v>
-      </c>
-      <c r="M12" t="s">
-        <v>34</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4</v>
-      </c>
-      <c r="O12" t="s">
-        <v>32</v>
-      </c>
-      <c r="P12" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>15</v>
-      </c>
-      <c r="R12" t="s">
-        <v>34</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="s">
+      <c r="U13" s="4" t="s">
         <v>54</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="8">
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="A3:U3"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="O5:Q5"/>
+    <mergeCell ref="R5:T5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -1252,67 +1308,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="5" t="s">
         <v>29</v>
       </c>
     </row>

--- a/projects/r-accessible-tables/demo_mikrozensus_accessible_fixed.xlsx
+++ b/projects/r-accessible-tables/demo_mikrozensus_accessible_fixed.xlsx
@@ -6,20 +6,402 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Main_Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="GT_Table" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Accessible_Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Documentation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Column_Mapping" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Summary_Statistics" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Accessibility_Guide" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Title: Mikrozensus Deutschland 2023 - Accessible Version</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Table subtitle: WCAG-compliant Excel table with GT formatting and structure</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Group: demographie</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Group: erwerbstätigkeit</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Group: wohnen</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Group: soziales</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Group: gesundheit</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Group: familie</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">demographie - personen id</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">demographie - größe (in tsd.)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">demographie - haushaltsgröße ∅</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">demographie - alter &gt; 65 jahre</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">erwerbstätigkeit - erwerbstätige (%)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">erwerbstätigkeit - arbeitslose rate</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">erwerbstätigkeit - einkommen ≥ 3000€</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">erwerbstätigkeit - netto &amp; brutto</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">wohnen - wohnfläche (m²)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">wohnen - miete: warm</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">wohnen - eigenheim ja/nein</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">soziales - fähigkeiten &amp; bildung</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">soziales - migrationshintergrund?</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">soziales - sprachen (anzahl)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">gesundheit - betreuungsbedürftig</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">gesundheit - krankenversicherung typ</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">gesundheit - arztbesuche/jahr</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">familie - familienstand: verheiratet</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">familie - kinder &lt; 18 jahre</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">familie - kinderbetreuung €</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">col</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Accessible version of Mikrozensus Deutschland 2023 - Accessible Version - Optimized for screen readers</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
-  <si>
-    <t xml:space="preserve">German Mikrozensus 2023 - Excel Compatible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixed version for Excel compatibility</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
+  <si>
+    <t xml:space="preserve">Mikrozensus Deutschland 2023 - Accessible Version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WCAG-compliant Excel table with GT formatting and structure</t>
   </si>
   <si>
     <t xml:space="preserve">demographie</t>
@@ -241,43 +623,166 @@
     <t xml:space="preserve">familie - kinderbetreuung €</t>
   </si>
   <si>
-    <t xml:space="preserve">Item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
+    <t xml:space="preserve">Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Original_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accessible_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sub_Column</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Has_Spanner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demographie_personen id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demographie_größe (in tsd.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demographie_haushaltsgröße ∅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demographie_alter &gt; 65 jahre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">erwerbstätigkeit_erwerbstätige (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">erwerbstätigkeit_arbeitslose rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">erwerbstätigkeit_einkommen ≥ 3000€</t>
+  </si>
+  <si>
+    <t xml:space="preserve">erwerbstätigkeit_netto &amp; brutto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wohnen_wohnfläche (m²)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wohnen_miete: warm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wohnen_eigenheim ja/nein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soziales_fähigkeiten &amp; bildung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soziales_migrationshintergrund?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soziales_sprachen (anzahl)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gesundheit_betreuungsbedürftig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gesundheit_krankenversicherung typ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gesundheit_arztbesuche/jahr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">familie_familienstand: verheiratet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">familie_kinder &lt; 18 jahre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">familie_kinderbetreuung €</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section</t>
   </si>
   <si>
     <t xml:space="preserve">Description</t>
   </si>
   <si>
-    <t xml:space="preserve">German micro census data with Excel-compatible formatting and accessibility features</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Columns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Created</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-20 14:26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Format</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excel-compatible accessible format</t>
+    <t xml:space="preserve">Overview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This Excel file has been optimized for accessibility and screen reader compatibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use Ctrl+Arrow keys to navigate efficiently. Headers are frozen for easy reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Screen_Readers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table headers include scope information. Use table navigation mode in JAWS/NVDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyboard_Access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tab navigation follows logical order. All content is keyboard accessible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data_Structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data is structured with clear headers and consistent formatting throughout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Color_Coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High contrast color scheme meets WCAG AA standards. No critical info conveyed by color alone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worksheet_Guide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GT_Table: Formatted view | Accessible_Data: Screen reader optimized | Column_Mapping: Structure info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For assistance with accessibility features, contact the document author</t>
   </si>
 </sst>
 </file>
@@ -285,7 +790,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -294,30 +799,42 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="16"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <b/>
     </font>
     <font>
       <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <i/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <b/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <b/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <b/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -327,6 +844,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF366092"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F0F0"/>
       </patternFill>
     </fill>
     <fill>
@@ -341,11 +863,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFF0F8FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE4B5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6E6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFB6C1"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -381,25 +918,53 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF4F81BD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF4F81BD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF4F81BD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF4F81BD"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -685,602 +1250,14 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="56.2025" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="17.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="20.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="19.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="20.74875" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="21.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="18.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="17.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="11.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="17.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="26.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="22.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="17.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="20.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="23.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="16.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="26.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="20.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="19.71" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="16.145" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="R6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="S6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="U6" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>85.4</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>850</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="S8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" s="4" t="n">
-        <v>450</v>
-      </c>
-      <c r="U8" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>92.1</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>1200</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q9" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="R9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="S9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" s="4" t="n">
-        <v>890</v>
-      </c>
-      <c r="U9" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>52.7</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>650</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="S10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>105.7</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>950</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q11" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="R11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="S11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" s="4" t="n">
-        <v>1200</v>
-      </c>
-      <c r="U11" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>67.8</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>69.1</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>89.6</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>1100</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O12" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="P12" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q12" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="R12" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="S12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" s="4" t="n">
-        <v>380</v>
-      </c>
-      <c r="U12" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>780</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O13" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="P13" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q13" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="R13" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="S13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A3:U3"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="O5:Q5"/>
-    <mergeCell ref="R5:T5"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac xr xr2 xr3" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3"> <sheetPr><tabColor rgb="FF0000FF"/></sheetPr><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac xr xr2 xr3" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3"> <pageSetUpPr fitToPage="1"/> <dimension ref="A1"/> <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/> <cols><col min="1" max="1" width="89.09375" hidden="0" customWidth="1"/><col min="2" max="2" width="20.74875" hidden="0" customWidth="1"/><col min="3" max="3" width="24.285" hidden="0" customWidth="1"/><col min="4" max="4" width="23.10625" hidden="0" customWidth="1"/><col min="5" max="5" width="21.9275" hidden="0" customWidth="1"/><col min="6" max="6" width="19.57" hidden="0" customWidth="1"/><col min="7" max="7" width="25.46375" hidden="0" customWidth="1"/><col min="8" max="8" width="21.9275" hidden="0" customWidth="1"/><col min="9" max="9" width="20.74875" hidden="0" customWidth="1"/><col min="10" max="10" width="13.67625" hidden="0" customWidth="1"/><col min="11" max="11" width="20.74875" hidden="0" customWidth="1"/><col min="12" max="12" width="31.3575" hidden="0" customWidth="1"/><col min="13" max="13" width="26.6425" hidden="0" customWidth="1"/><col min="14" max="14" width="20.74875" hidden="0" customWidth="1"/><col min="15" max="15" width="24.285" hidden="0" customWidth="1"/><col min="16" max="16" width="27.82125" hidden="0" customWidth="1"/><col min="17" max="17" width="19.57" hidden="0" customWidth="1"/><col min="18" max="18" width="31.3575" hidden="0" customWidth="1"/><col min="19" max="19" width="24.285" hidden="0" customWidth="1"/><col min="20" max="20" width="23.10625" hidden="0" customWidth="1"/><col min="21" max="21" width="18.71" hidden="0" customWidth="1"/></cols><sheetData><row r="1"><c r="A1" s="1" t="s"><v>0</v></c><c r="B1" s="1"/><c r="C1" s="1"/><c r="D1" s="1"/><c r="E1" s="1"/><c r="F1" s="1"/><c r="G1" s="1"/><c r="H1" s="1"/><c r="I1" s="1"/><c r="J1" s="1"/><c r="K1" s="1"/><c r="L1" s="1"/><c r="M1" s="1"/><c r="N1" s="1"/><c r="O1" s="1"/><c r="P1" s="1"/><c r="Q1" s="1"/><c r="R1" s="1"/><c r="S1" s="1"/><c r="T1" s="1"/><c r="U1" s="1"/></row><row r="2"><c r="A2" s="2" t="s"><v>1</v></c><c r="B2" s="2"/><c r="C2" s="2"/><c r="D2" s="2"/><c r="E2" s="2"/><c r="F2" s="2"/><c r="G2" s="2"/><c r="H2" s="2"/><c r="I2" s="2"/><c r="J2" s="2"/><c r="K2" s="2"/><c r="L2" s="2"/><c r="M2" s="2"/><c r="N2" s="2"/><c r="O2" s="2"/><c r="P2" s="2"/><c r="Q2" s="2"/><c r="R2" s="2"/><c r="S2" s="2"/><c r="T2" s="2"/><c r="U2" s="2"/></row><row r="4"><c r="A4" s="3" t="s"><v>2</v></c><c r="B4" s="3" t="s"><v>3</v></c><c r="C4" s="3" t="s"><v>3</v></c><c r="D4" s="3" t="s"><v>3</v></c><c r="E4" s="3" t="s"><v>4</v></c><c r="F4" s="3" t="s"><v>3</v></c><c r="G4" s="3" t="s"><v>3</v></c><c r="H4" s="3" t="s"><v>3</v></c><c r="I4" s="3" t="s"><v>5</v></c><c r="J4" s="3" t="s"><v>3</v></c><c r="K4" s="3" t="s"><v>3</v></c><c r="L4" s="3" t="s"><v>6</v></c><c r="M4" s="3" t="s"><v>3</v></c><c r="N4" s="3" t="s"><v>3</v></c><c r="O4" s="3" t="s"><v>7</v></c><c r="P4" s="3" t="s"><v>3</v></c><c r="Q4" s="3" t="s"><v>3</v></c><c r="R4" s="3" t="s"><v>8</v></c><c r="S4" s="3" t="s"><v>3</v></c><c r="T4" s="3" t="s"><v>3</v></c><c r="U4" s="3" t="s"><v>3</v></c></row><row r="5"><c r="A5" s="4" t="s"><v>9</v></c><c r="B5" s="4" t="s"><v>10</v></c><c r="C5" s="4" t="s"><v>11</v></c><c r="D5" s="4" t="s"><v>12</v></c><c r="E5" s="4" t="s"><v>13</v></c><c r="F5" s="4" t="s"><v>14</v></c><c r="G5" s="4" t="s"><v>15</v></c><c r="H5" s="4" t="s"><v>16</v></c><c r="I5" s="4" t="s"><v>17</v></c><c r="J5" s="4" t="s"><v>18</v></c><c r="K5" s="4" t="s"><v>19</v></c><c r="L5" s="4" t="s"><v>20</v></c><c r="M5" s="4" t="s"><v>21</v></c><c r="N5" s="4" t="s"><v>22</v></c><c r="O5" s="4" t="s"><v>23</v></c><c r="P5" s="4" t="s"><v>24</v></c><c r="Q5" s="4" t="s"><v>25</v></c><c r="R5" s="4" t="s"><v>26</v></c><c r="S5" s="4" t="s"><v>27</v></c><c r="T5" s="4" t="s"><v>28</v></c><c r="U5" s="4" t="s"><v>29</v></c></row><row r="6"><c r="A6" s="5" t="s"><v>30</v></c><c r="B6" s="6" t="n"><v>45.2</v></c><c r="C6" s="6" t="n"><v>2.1</v></c><c r="D6" s="6" t="n"><v>18.5</v></c><c r="E6" s="6" t="n"><v>64.8</v></c><c r="F6" s="6" t="n"><v>5.8</v></c><c r="G6" s="6" t="n"><v>15.2</v></c><c r="H6" s="5" t="s"><v>31</v></c><c r="I6" s="6" t="n"><v>85.4</v></c><c r="J6" s="6" t="n"><v>850</v></c><c r="K6" s="5" t="s"><v>32</v></c><c r="L6" s="5" t="s"><v>33</v></c><c r="M6" s="5" t="s"><v>34</v></c><c r="N6" s="6" t="n"><v>2</v></c><c r="O6" s="5" t="s"><v>32</v></c><c r="P6" s="5" t="s"><v>35</v></c><c r="Q6" s="6" t="n"><v>4</v></c><c r="R6" s="5" t="s"><v>34</v></c><c r="S6" s="6" t="n"><v>1</v></c><c r="T6" s="6" t="n"><v>450</v></c><c r="U6" s="5" t="s"><v>36</v></c></row><row r="7"><c r="A7" s="5" t="s"><v>37</v></c><c r="B7" s="6" t="n"><v>38.1</v></c><c r="C7" s="6" t="n"><v>2.8</v></c><c r="D7" s="6" t="n"><v>22.3</v></c><c r="E7" s="6" t="n"><v>58.2</v></c><c r="F7" s="6" t="n"><v>7.2</v></c><c r="G7" s="6" t="n"><v>12.8</v></c><c r="H7" s="5" t="s"><v>38</v></c><c r="I7" s="6" t="n"><v>92.1</v></c><c r="J7" s="6" t="n"><v>1200</v></c><c r="K7" s="5" t="s"><v>34</v></c><c r="L7" s="5" t="s"><v>39</v></c><c r="M7" s="5" t="s"><v>32</v></c><c r="N7" s="6" t="n"><v>1</v></c><c r="O7" s="5" t="s"><v>34</v></c><c r="P7" s="5" t="s"><v>40</v></c><c r="Q7" s="6" t="n"><v>12</v></c><c r="R7" s="5" t="s"><v>34</v></c><c r="S7" s="6" t="n"><v>2</v></c><c r="T7" s="6" t="n"><v>890</v></c><c r="U7" s="5" t="s"><v>41</v></c></row><row r="8"><c r="A8" s="5" t="s"><v>42</v></c><c r="B8" s="6" t="n"><v>52.7</v></c><c r="C8" s="6" t="n"><v>1</v></c><c r="D8" s="6" t="n"><v>31.2</v></c><c r="E8" s="6" t="n"><v>71.3</v></c><c r="F8" s="6" t="n"><v>4.1</v></c><c r="G8" s="6" t="n"><v>18.6</v></c><c r="H8" s="5" t="s"><v>43</v></c><c r="I8" s="6" t="n"><v>78.3</v></c><c r="J8" s="6" t="n"><v>650</v></c><c r="K8" s="5" t="s"><v>32</v></c><c r="L8" s="5" t="s"><v>33</v></c><c r="M8" s="5" t="s"><v>34</v></c><c r="N8" s="6" t="n"><v>3</v></c><c r="O8" s="5" t="s"><v>32</v></c><c r="P8" s="5" t="s"><v>35</v></c><c r="Q8" s="6" t="n"><v>2</v></c><c r="R8" s="5" t="s"><v>32</v></c><c r="S8" s="6" t="n"><v>0</v></c><c r="T8" s="6" t="n"><v>0</v></c><c r="U8" s="5" t="s"><v>44</v></c></row><row r="9"><c r="A9" s="5" t="s"><v>45</v></c><c r="B9" s="6" t="n"><v>29.3</v></c><c r="C9" s="6" t="n"><v>3.4</v></c><c r="D9" s="6" t="n"><v>15.8</v></c><c r="E9" s="6" t="n"><v>55.9</v></c><c r="F9" s="6" t="n"><v>9.5</v></c><c r="G9" s="6" t="n"><v>8.4</v></c><c r="H9" s="5" t="s"><v>46</v></c><c r="I9" s="6" t="n"><v>105.7</v></c><c r="J9" s="6" t="n"><v>950</v></c><c r="K9" s="5" t="s"><v>34</v></c><c r="L9" s="5" t="s"><v>47</v></c><c r="M9" s="5" t="s"><v>32</v></c><c r="N9" s="6" t="n"><v>1</v></c><c r="O9" s="5" t="s"><v>32</v></c><c r="P9" s="5" t="s"><v>35</v></c><c r="Q9" s="6" t="n"><v>8</v></c><c r="R9" s="5" t="s"><v>34</v></c><c r="S9" s="6" t="n"><v>3</v></c><c r="T9" s="6" t="n"><v>1200</v></c><c r="U9" s="5" t="s"><v>48</v></c></row><row r="10"><c r="A10" s="5" t="s"><v>49</v></c><c r="B10" s="6" t="n"><v>67.8</v></c><c r="C10" s="6" t="n"><v>2.5</v></c><c r="D10" s="6" t="n"><v>28.7</v></c><c r="E10" s="6" t="n"><v>69.1</v></c><c r="F10" s="6" t="n"><v>6.3</v></c><c r="G10" s="6" t="n"><v>16.7</v></c><c r="H10" s="5" t="s"><v>50</v></c><c r="I10" s="6" t="n"><v>89.6</v></c><c r="J10" s="6" t="n"><v>1100</v></c><c r="K10" s="5" t="s"><v>34</v></c><c r="L10" s="5" t="s"><v>33</v></c><c r="M10" s="5" t="s"><v>32</v></c><c r="N10" s="6" t="n"><v>2</v></c><c r="O10" s="5" t="s"><v>34</v></c><c r="P10" s="5" t="s"><v>40</v></c><c r="Q10" s="6" t="n"><v>6</v></c><c r="R10" s="5" t="s"><v>32</v></c><c r="S10" s="6" t="n"><v>1</v></c><c r="T10" s="6" t="n"><v>380</v></c><c r="U10" s="5" t="s"><v>51</v></c></row><row r="11"><c r="A11" s="5" t="s"><v>52</v></c><c r="B11" s="6" t="n"><v>41.5</v></c><c r="C11" s="6" t="n"><v>1.7</v></c><c r="D11" s="6" t="n"><v>25.1</v></c><c r="E11" s="6" t="n"><v>62.4</v></c><c r="F11" s="6" t="n"><v>8.1</v></c><c r="G11" s="6" t="n"><v>11.9</v></c><c r="H11" s="5" t="s"><v>53</v></c><c r="I11" s="6" t="n"><v>73.2</v></c><c r="J11" s="6" t="n"><v>780</v></c><c r="K11" s="5" t="s"><v>32</v></c><c r="L11" s="5" t="s"><v>39</v></c><c r="M11" s="5" t="s"><v>34</v></c><c r="N11" s="6" t="n"><v>4</v></c><c r="O11" s="5" t="s"><v>32</v></c><c r="P11" s="5" t="s"><v>35</v></c><c r="Q11" s="6" t="n"><v>15</v></c><c r="R11" s="5" t="s"><v>34</v></c><c r="S11" s="6" t="n"><v>0</v></c><c r="T11" s="6" t="n"><v>0</v></c><c r="U11" s="5" t="s"><v>54</v></c></row></sheetData><mergeCells count="8"><mergeCell ref="A1:U1"/><mergeCell ref="A2:U2"/><mergeCell ref="A4:D4"/><mergeCell ref="E4:H4"/><mergeCell ref="I4:K4"/><mergeCell ref="L4:N4"/><mergeCell ref="O4:Q4"/><mergeCell ref="R4:T4"/></mergeCells><pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/><pageSetup paperSize="9" orientation="landscape" scale = "100" fitToWidth="1" fitToHeight="0" horizontalDpi="300" verticalDpi="300" r:id="rId2"/><legacyDrawing r:id="rIdvml"/></worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <sheetPr>
+    <tabColor rgb="FF00FF00"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
@@ -1308,67 +1285,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="7" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1760,6 +1737,469 @@
       </c>
       <c r="U7" t="s">
         <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <legacyDrawing r:id="rIdvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <sheetPr>
+    <tabColor rgb="FFFFA500"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="8.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="39.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="41.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="17.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="26.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" t="s">
+        <v>101</v>
+      </c>
+      <c r="E22" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1768,69 +2208,490 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <sheetPr>
+    <tabColor rgb="FFA020F0"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="50.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="39.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="4.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="6.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="6.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="6.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="5.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="5.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1" t="s">
-        <v>76</v>
+      <c r="A1" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B2" t="s">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="B2" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.35</v>
+      </c>
+      <c r="E2" t="n">
+        <v>45.7666666666667</v>
+      </c>
+      <c r="F2" t="n">
+        <v>50.825</v>
+      </c>
+      <c r="G2" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>13.2815159777288</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" t="s">
-        <v>79</v>
+        <v>83</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.845576726264388</v>
+      </c>
+      <c r="I3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" t="s">
-        <v>81</v>
+        <v>84</v>
+      </c>
+      <c r="B4" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="C4" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="D4" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5.90863774486133</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B5" t="s">
-        <v>83</v>
+        <v>85</v>
+      </c>
+      <c r="B5" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="C5" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="D5" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>63.6166666666667</v>
+      </c>
+      <c r="F5" t="n">
+        <v>68.025</v>
+      </c>
+      <c r="G5" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6.01445481042685</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>84</v>
-      </c>
-      <c r="B6" t="s">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5.925</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6.83333333333333</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7.875</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.88007092064812</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>12.125</v>
+      </c>
+      <c r="D7" t="n">
+        <v>14</v>
+      </c>
+      <c r="E7" t="n">
+        <v>13.9333333333333</v>
+      </c>
+      <c r="F7" t="n">
+        <v>16.325</v>
+      </c>
+      <c r="G7" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.66260380967785</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>80.075</v>
+      </c>
+      <c r="D8" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>87.3833333333333</v>
+      </c>
+      <c r="F8" t="n">
+        <v>91.475</v>
+      </c>
+      <c r="G8" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>11.404107447173</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" t="n">
+        <v>650</v>
+      </c>
+      <c r="C9" t="n">
+        <v>797.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>900</v>
+      </c>
+      <c r="E9" t="n">
+        <v>921.666666666667</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1062.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H9" t="n">
+        <v>204.491238606124</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.16666666666667</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.16904519445001</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>7.83333333333333</v>
+      </c>
+      <c r="F11" t="n">
+        <v>11</v>
+      </c>
+      <c r="G11" t="n">
+        <v>15</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.91596040125088</v>
+      </c>
+      <c r="I11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.16666666666667</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.16904519445001</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>95</v>
+      </c>
+      <c r="D13" t="n">
+        <v>415</v>
+      </c>
+      <c r="E13" t="n">
+        <v>486.666666666667</v>
+      </c>
+      <c r="F13" t="n">
+        <v>780</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H13" t="n">
+        <v>481.234523560672</v>
+      </c>
+      <c r="I13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="20.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="80.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>123</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/projects/r-accessible-tables/demo_mikrozensus_accessible_fixed.xlsx
+++ b/projects/r-accessible-tables/demo_mikrozensus_accessible_fixed.xlsx
@@ -9,394 +9,13 @@
     <sheet name="GT_Table" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Accessible_Data" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Column_Mapping" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Summary_Statistics" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Accessibility_Guide" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Accessibility_Guide" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author/>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">Title: Mikrozensus Deutschland 2023 - Accessible Version</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A2" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">Table subtitle: WCAG-compliant Excel table with GT formatting and structure</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A4" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">Group: demographie</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E4" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">Group: erwerbstätigkeit</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I4" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">Group: wohnen</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L4" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">Group: soziales</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O4" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">Group: gesundheit</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="R4" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">Group: familie</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A5" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">demographie - personen id</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B5" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">demographie - größe (in tsd.)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C5" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">demographie - haushaltsgröße ∅</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D5" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">demographie - alter &gt; 65 jahre</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E5" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">erwerbstätigkeit - erwerbstätige (%)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F5" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">erwerbstätigkeit - arbeitslose rate</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G5" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">erwerbstätigkeit - einkommen ≥ 3000€</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H5" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">erwerbstätigkeit - netto &amp; brutto</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I5" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">wohnen - wohnfläche (m²)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J5" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">wohnen - miete: warm</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K5" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">wohnen - eigenheim ja/nein</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L5" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">soziales - fähigkeiten &amp; bildung</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M5" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">soziales - migrationshintergrund?</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N5" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">soziales - sprachen (anzahl)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O5" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">gesundheit - betreuungsbedürftig</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P5" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">gesundheit - krankenversicherung typ</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q5" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">gesundheit - arztbesuche/jahr</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="R5" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">familie - familienstand: verheiratet</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S5" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">familie - kinder &lt; 18 jahre</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T5" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">familie - kinderbetreuung €</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U5" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">col</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author/>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">Accessible version of Mikrozensus Deutschland 2023 - Accessible Version - Optimized for screen readers</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
   <si>
     <t xml:space="preserve">Mikrozensus Deutschland 2023 - Accessible Version</t>
   </si>
@@ -704,33 +323,6 @@
     <t xml:space="preserve">None</t>
   </si>
   <si>
-    <t xml:space="preserve">Column</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
     <t xml:space="preserve">Section</t>
   </si>
   <si>
@@ -740,19 +332,19 @@
     <t xml:space="preserve">Overview</t>
   </si>
   <si>
-    <t xml:space="preserve">This Excel file has been optimized for accessibility and screen reader compatibility</t>
+    <t xml:space="preserve">This Excel file is optimized for accessibility and screen readers</t>
   </si>
   <si>
     <t xml:space="preserve">Navigation</t>
   </si>
   <si>
-    <t xml:space="preserve">Use Ctrl+Arrow keys to navigate efficiently. Headers are frozen for easy reference</t>
+    <t xml:space="preserve">Use Ctrl+Arrow keys to navigate. Headers are frozen for reference</t>
   </si>
   <si>
     <t xml:space="preserve">Screen_Readers</t>
   </si>
   <si>
-    <t xml:space="preserve">Table headers include scope information. Use table navigation mode in JAWS/NVDA</t>
+    <t xml:space="preserve">Enable table navigation mode in JAWS/NVDA for best experience</t>
   </si>
   <si>
     <t xml:space="preserve">Keyboard_Access</t>
@@ -761,28 +353,28 @@
     <t xml:space="preserve">Tab navigation follows logical order. All content is keyboard accessible</t>
   </si>
   <si>
-    <t xml:space="preserve">Data_Structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data is structured with clear headers and consistent formatting throughout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Color_Coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High contrast color scheme meets WCAG AA standards. No critical info conveyed by color alone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Worksheet_Guide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GT_Table: Formatted view | Accessible_Data: Screen reader optimized | Column_Mapping: Structure info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For assistance with accessibility features, contact the document author</t>
+    <t xml:space="preserve">Worksheets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GT_Table: Formatted view | Accessible_Data: Simple structure | Column_Mapping: Documentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GT_Table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main table with GT-style formatting and spanner headers showing column groups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accessible_Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Screen reader optimized with simple headers and no merged cells in data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column_Mapping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shows original column names, accessible names, and structure information</t>
   </si>
 </sst>
 </file>
@@ -834,7 +426,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -869,11 +461,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFE4B5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6E6FA"/>
       </patternFill>
     </fill>
     <fill>
@@ -941,30 +528,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1250,14 +833,622 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac xr xr2 xr3" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3"> <sheetPr><tabColor rgb="FF0000FF"/></sheetPr><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac xr xr2 xr3" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3"> <pageSetUpPr fitToPage="1"/> <dimension ref="A1"/> <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/> <cols><col min="1" max="1" width="89.09375" hidden="0" customWidth="1"/><col min="2" max="2" width="20.74875" hidden="0" customWidth="1"/><col min="3" max="3" width="24.285" hidden="0" customWidth="1"/><col min="4" max="4" width="23.10625" hidden="0" customWidth="1"/><col min="5" max="5" width="21.9275" hidden="0" customWidth="1"/><col min="6" max="6" width="19.57" hidden="0" customWidth="1"/><col min="7" max="7" width="25.46375" hidden="0" customWidth="1"/><col min="8" max="8" width="21.9275" hidden="0" customWidth="1"/><col min="9" max="9" width="20.74875" hidden="0" customWidth="1"/><col min="10" max="10" width="13.67625" hidden="0" customWidth="1"/><col min="11" max="11" width="20.74875" hidden="0" customWidth="1"/><col min="12" max="12" width="31.3575" hidden="0" customWidth="1"/><col min="13" max="13" width="26.6425" hidden="0" customWidth="1"/><col min="14" max="14" width="20.74875" hidden="0" customWidth="1"/><col min="15" max="15" width="24.285" hidden="0" customWidth="1"/><col min="16" max="16" width="27.82125" hidden="0" customWidth="1"/><col min="17" max="17" width="19.57" hidden="0" customWidth="1"/><col min="18" max="18" width="31.3575" hidden="0" customWidth="1"/><col min="19" max="19" width="24.285" hidden="0" customWidth="1"/><col min="20" max="20" width="23.10625" hidden="0" customWidth="1"/><col min="21" max="21" width="18.71" hidden="0" customWidth="1"/></cols><sheetData><row r="1"><c r="A1" s="1" t="s"><v>0</v></c><c r="B1" s="1"/><c r="C1" s="1"/><c r="D1" s="1"/><c r="E1" s="1"/><c r="F1" s="1"/><c r="G1" s="1"/><c r="H1" s="1"/><c r="I1" s="1"/><c r="J1" s="1"/><c r="K1" s="1"/><c r="L1" s="1"/><c r="M1" s="1"/><c r="N1" s="1"/><c r="O1" s="1"/><c r="P1" s="1"/><c r="Q1" s="1"/><c r="R1" s="1"/><c r="S1" s="1"/><c r="T1" s="1"/><c r="U1" s="1"/></row><row r="2"><c r="A2" s="2" t="s"><v>1</v></c><c r="B2" s="2"/><c r="C2" s="2"/><c r="D2" s="2"/><c r="E2" s="2"/><c r="F2" s="2"/><c r="G2" s="2"/><c r="H2" s="2"/><c r="I2" s="2"/><c r="J2" s="2"/><c r="K2" s="2"/><c r="L2" s="2"/><c r="M2" s="2"/><c r="N2" s="2"/><c r="O2" s="2"/><c r="P2" s="2"/><c r="Q2" s="2"/><c r="R2" s="2"/><c r="S2" s="2"/><c r="T2" s="2"/><c r="U2" s="2"/></row><row r="4"><c r="A4" s="3" t="s"><v>2</v></c><c r="B4" s="3" t="s"><v>3</v></c><c r="C4" s="3" t="s"><v>3</v></c><c r="D4" s="3" t="s"><v>3</v></c><c r="E4" s="3" t="s"><v>4</v></c><c r="F4" s="3" t="s"><v>3</v></c><c r="G4" s="3" t="s"><v>3</v></c><c r="H4" s="3" t="s"><v>3</v></c><c r="I4" s="3" t="s"><v>5</v></c><c r="J4" s="3" t="s"><v>3</v></c><c r="K4" s="3" t="s"><v>3</v></c><c r="L4" s="3" t="s"><v>6</v></c><c r="M4" s="3" t="s"><v>3</v></c><c r="N4" s="3" t="s"><v>3</v></c><c r="O4" s="3" t="s"><v>7</v></c><c r="P4" s="3" t="s"><v>3</v></c><c r="Q4" s="3" t="s"><v>3</v></c><c r="R4" s="3" t="s"><v>8</v></c><c r="S4" s="3" t="s"><v>3</v></c><c r="T4" s="3" t="s"><v>3</v></c><c r="U4" s="3" t="s"><v>3</v></c></row><row r="5"><c r="A5" s="4" t="s"><v>9</v></c><c r="B5" s="4" t="s"><v>10</v></c><c r="C5" s="4" t="s"><v>11</v></c><c r="D5" s="4" t="s"><v>12</v></c><c r="E5" s="4" t="s"><v>13</v></c><c r="F5" s="4" t="s"><v>14</v></c><c r="G5" s="4" t="s"><v>15</v></c><c r="H5" s="4" t="s"><v>16</v></c><c r="I5" s="4" t="s"><v>17</v></c><c r="J5" s="4" t="s"><v>18</v></c><c r="K5" s="4" t="s"><v>19</v></c><c r="L5" s="4" t="s"><v>20</v></c><c r="M5" s="4" t="s"><v>21</v></c><c r="N5" s="4" t="s"><v>22</v></c><c r="O5" s="4" t="s"><v>23</v></c><c r="P5" s="4" t="s"><v>24</v></c><c r="Q5" s="4" t="s"><v>25</v></c><c r="R5" s="4" t="s"><v>26</v></c><c r="S5" s="4" t="s"><v>27</v></c><c r="T5" s="4" t="s"><v>28</v></c><c r="U5" s="4" t="s"><v>29</v></c></row><row r="6"><c r="A6" s="5" t="s"><v>30</v></c><c r="B6" s="6" t="n"><v>45.2</v></c><c r="C6" s="6" t="n"><v>2.1</v></c><c r="D6" s="6" t="n"><v>18.5</v></c><c r="E6" s="6" t="n"><v>64.8</v></c><c r="F6" s="6" t="n"><v>5.8</v></c><c r="G6" s="6" t="n"><v>15.2</v></c><c r="H6" s="5" t="s"><v>31</v></c><c r="I6" s="6" t="n"><v>85.4</v></c><c r="J6" s="6" t="n"><v>850</v></c><c r="K6" s="5" t="s"><v>32</v></c><c r="L6" s="5" t="s"><v>33</v></c><c r="M6" s="5" t="s"><v>34</v></c><c r="N6" s="6" t="n"><v>2</v></c><c r="O6" s="5" t="s"><v>32</v></c><c r="P6" s="5" t="s"><v>35</v></c><c r="Q6" s="6" t="n"><v>4</v></c><c r="R6" s="5" t="s"><v>34</v></c><c r="S6" s="6" t="n"><v>1</v></c><c r="T6" s="6" t="n"><v>450</v></c><c r="U6" s="5" t="s"><v>36</v></c></row><row r="7"><c r="A7" s="5" t="s"><v>37</v></c><c r="B7" s="6" t="n"><v>38.1</v></c><c r="C7" s="6" t="n"><v>2.8</v></c><c r="D7" s="6" t="n"><v>22.3</v></c><c r="E7" s="6" t="n"><v>58.2</v></c><c r="F7" s="6" t="n"><v>7.2</v></c><c r="G7" s="6" t="n"><v>12.8</v></c><c r="H7" s="5" t="s"><v>38</v></c><c r="I7" s="6" t="n"><v>92.1</v></c><c r="J7" s="6" t="n"><v>1200</v></c><c r="K7" s="5" t="s"><v>34</v></c><c r="L7" s="5" t="s"><v>39</v></c><c r="M7" s="5" t="s"><v>32</v></c><c r="N7" s="6" t="n"><v>1</v></c><c r="O7" s="5" t="s"><v>34</v></c><c r="P7" s="5" t="s"><v>40</v></c><c r="Q7" s="6" t="n"><v>12</v></c><c r="R7" s="5" t="s"><v>34</v></c><c r="S7" s="6" t="n"><v>2</v></c><c r="T7" s="6" t="n"><v>890</v></c><c r="U7" s="5" t="s"><v>41</v></c></row><row r="8"><c r="A8" s="5" t="s"><v>42</v></c><c r="B8" s="6" t="n"><v>52.7</v></c><c r="C8" s="6" t="n"><v>1</v></c><c r="D8" s="6" t="n"><v>31.2</v></c><c r="E8" s="6" t="n"><v>71.3</v></c><c r="F8" s="6" t="n"><v>4.1</v></c><c r="G8" s="6" t="n"><v>18.6</v></c><c r="H8" s="5" t="s"><v>43</v></c><c r="I8" s="6" t="n"><v>78.3</v></c><c r="J8" s="6" t="n"><v>650</v></c><c r="K8" s="5" t="s"><v>32</v></c><c r="L8" s="5" t="s"><v>33</v></c><c r="M8" s="5" t="s"><v>34</v></c><c r="N8" s="6" t="n"><v>3</v></c><c r="O8" s="5" t="s"><v>32</v></c><c r="P8" s="5" t="s"><v>35</v></c><c r="Q8" s="6" t="n"><v>2</v></c><c r="R8" s="5" t="s"><v>32</v></c><c r="S8" s="6" t="n"><v>0</v></c><c r="T8" s="6" t="n"><v>0</v></c><c r="U8" s="5" t="s"><v>44</v></c></row><row r="9"><c r="A9" s="5" t="s"><v>45</v></c><c r="B9" s="6" t="n"><v>29.3</v></c><c r="C9" s="6" t="n"><v>3.4</v></c><c r="D9" s="6" t="n"><v>15.8</v></c><c r="E9" s="6" t="n"><v>55.9</v></c><c r="F9" s="6" t="n"><v>9.5</v></c><c r="G9" s="6" t="n"><v>8.4</v></c><c r="H9" s="5" t="s"><v>46</v></c><c r="I9" s="6" t="n"><v>105.7</v></c><c r="J9" s="6" t="n"><v>950</v></c><c r="K9" s="5" t="s"><v>34</v></c><c r="L9" s="5" t="s"><v>47</v></c><c r="M9" s="5" t="s"><v>32</v></c><c r="N9" s="6" t="n"><v>1</v></c><c r="O9" s="5" t="s"><v>32</v></c><c r="P9" s="5" t="s"><v>35</v></c><c r="Q9" s="6" t="n"><v>8</v></c><c r="R9" s="5" t="s"><v>34</v></c><c r="S9" s="6" t="n"><v>3</v></c><c r="T9" s="6" t="n"><v>1200</v></c><c r="U9" s="5" t="s"><v>48</v></c></row><row r="10"><c r="A10" s="5" t="s"><v>49</v></c><c r="B10" s="6" t="n"><v>67.8</v></c><c r="C10" s="6" t="n"><v>2.5</v></c><c r="D10" s="6" t="n"><v>28.7</v></c><c r="E10" s="6" t="n"><v>69.1</v></c><c r="F10" s="6" t="n"><v>6.3</v></c><c r="G10" s="6" t="n"><v>16.7</v></c><c r="H10" s="5" t="s"><v>50</v></c><c r="I10" s="6" t="n"><v>89.6</v></c><c r="J10" s="6" t="n"><v>1100</v></c><c r="K10" s="5" t="s"><v>34</v></c><c r="L10" s="5" t="s"><v>33</v></c><c r="M10" s="5" t="s"><v>32</v></c><c r="N10" s="6" t="n"><v>2</v></c><c r="O10" s="5" t="s"><v>34</v></c><c r="P10" s="5" t="s"><v>40</v></c><c r="Q10" s="6" t="n"><v>6</v></c><c r="R10" s="5" t="s"><v>32</v></c><c r="S10" s="6" t="n"><v>1</v></c><c r="T10" s="6" t="n"><v>380</v></c><c r="U10" s="5" t="s"><v>51</v></c></row><row r="11"><c r="A11" s="5" t="s"><v>52</v></c><c r="B11" s="6" t="n"><v>41.5</v></c><c r="C11" s="6" t="n"><v>1.7</v></c><c r="D11" s="6" t="n"><v>25.1</v></c><c r="E11" s="6" t="n"><v>62.4</v></c><c r="F11" s="6" t="n"><v>8.1</v></c><c r="G11" s="6" t="n"><v>11.9</v></c><c r="H11" s="5" t="s"><v>53</v></c><c r="I11" s="6" t="n"><v>73.2</v></c><c r="J11" s="6" t="n"><v>780</v></c><c r="K11" s="5" t="s"><v>32</v></c><c r="L11" s="5" t="s"><v>39</v></c><c r="M11" s="5" t="s"><v>34</v></c><c r="N11" s="6" t="n"><v>4</v></c><c r="O11" s="5" t="s"><v>32</v></c><c r="P11" s="5" t="s"><v>35</v></c><c r="Q11" s="6" t="n"><v>15</v></c><c r="R11" s="5" t="s"><v>34</v></c><c r="S11" s="6" t="n"><v>0</v></c><c r="T11" s="6" t="n"><v>0</v></c><c r="U11" s="5" t="s"><v>54</v></c></row></sheetData><mergeCells count="8"><mergeCell ref="A1:U1"/><mergeCell ref="A2:U2"/><mergeCell ref="A4:D4"/><mergeCell ref="E4:H4"/><mergeCell ref="I4:K4"/><mergeCell ref="L4:N4"/><mergeCell ref="O4:Q4"/><mergeCell ref="R4:T4"/></mergeCells><pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/><pageSetup paperSize="9" orientation="landscape" scale = "100" fitToWidth="1" fitToHeight="0" horizontalDpi="300" verticalDpi="300" r:id="rId2"/><legacyDrawing r:id="rIdvml"/></worksheet>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="89.09375" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20.74875" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="24.285" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="23.10625" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="21.9275" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="19.57" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="25.46375" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="21.9275" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="20.74875" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="13.67625" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="20.74875" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="31.3575" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="26.6425" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="20.74875" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="24.285" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="27.82125" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="19.57" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="31.3575" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="24.285" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="23.10625" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>85.4</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>850</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="U6" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>92.1</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="R7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="S7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" s="5" t="n">
+        <v>890</v>
+      </c>
+      <c r="U7" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>650</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="S8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>950</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="S9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" s="5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="U9" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>69.1</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>89.6</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>1100</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="S10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" s="5" t="n">
+        <v>380</v>
+      </c>
+      <c r="U10" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>780</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="R11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="S11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="R4:T4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <sheetPr>
-    <tabColor rgb="FF00FF00"/>
-  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
@@ -1285,67 +1476,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="Q1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="S1" s="7" t="s">
+      <c r="S1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="T1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="U1" s="7" t="s">
+      <c r="U1" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1742,15 +1933,11 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-  <legacyDrawing r:id="rIdvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <sheetPr>
-    <tabColor rgb="FFFFA500"/>
-  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
@@ -1763,22 +1950,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>80</v>
       </c>
     </row>
@@ -2210,411 +2397,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <sheetPr>
-    <tabColor rgb="FFA020F0"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="39.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="4.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="6.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="6.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="6.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="5.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="5.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.95</v>
-      </c>
-      <c r="D2" t="n">
-        <v>43.35</v>
-      </c>
-      <c r="E2" t="n">
-        <v>45.7666666666667</v>
-      </c>
-      <c r="F2" t="n">
-        <v>50.825</v>
-      </c>
-      <c r="G2" t="n">
-        <v>67.8</v>
-      </c>
-      <c r="H2" t="n">
-        <v>13.2815159777288</v>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2.725</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.845576726264388</v>
-      </c>
-      <c r="I3" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B4" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="C4" t="n">
-        <v>19.45</v>
-      </c>
-      <c r="D4" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="E4" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="F4" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="G4" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>5.90863774486133</v>
-      </c>
-      <c r="I4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B5" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="C5" t="n">
-        <v>59.25</v>
-      </c>
-      <c r="D5" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="E5" t="n">
-        <v>63.6166666666667</v>
-      </c>
-      <c r="F5" t="n">
-        <v>68.025</v>
-      </c>
-      <c r="G5" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6.01445481042685</v>
-      </c>
-      <c r="I5" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>86</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>5.925</v>
-      </c>
-      <c r="D6" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="E6" t="n">
-        <v>6.83333333333333</v>
-      </c>
-      <c r="F6" t="n">
-        <v>7.875</v>
-      </c>
-      <c r="G6" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.88007092064812</v>
-      </c>
-      <c r="I6" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="C7" t="n">
-        <v>12.125</v>
-      </c>
-      <c r="D7" t="n">
-        <v>14</v>
-      </c>
-      <c r="E7" t="n">
-        <v>13.9333333333333</v>
-      </c>
-      <c r="F7" t="n">
-        <v>16.325</v>
-      </c>
-      <c r="G7" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.66260380967785</v>
-      </c>
-      <c r="I7" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B8" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="C8" t="n">
-        <v>80.075</v>
-      </c>
-      <c r="D8" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="E8" t="n">
-        <v>87.3833333333333</v>
-      </c>
-      <c r="F8" t="n">
-        <v>91.475</v>
-      </c>
-      <c r="G8" t="n">
-        <v>105.7</v>
-      </c>
-      <c r="H8" t="n">
-        <v>11.404107447173</v>
-      </c>
-      <c r="I8" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>90</v>
-      </c>
-      <c r="B9" t="n">
-        <v>650</v>
-      </c>
-      <c r="C9" t="n">
-        <v>797.5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>900</v>
-      </c>
-      <c r="E9" t="n">
-        <v>921.666666666667</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1062.5</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1200</v>
-      </c>
-      <c r="H9" t="n">
-        <v>204.491238606124</v>
-      </c>
-      <c r="I9" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>94</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2.16666666666667</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="G10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.16904519445001</v>
-      </c>
-      <c r="I10" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>97</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>7</v>
-      </c>
-      <c r="E11" t="n">
-        <v>7.83333333333333</v>
-      </c>
-      <c r="F11" t="n">
-        <v>11</v>
-      </c>
-      <c r="G11" t="n">
-        <v>15</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4.91596040125088</v>
-      </c>
-      <c r="I11" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>99</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1.16666666666667</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="G12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.16904519445001</v>
-      </c>
-      <c r="I12" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>95</v>
-      </c>
-      <c r="D13" t="n">
-        <v>415</v>
-      </c>
-      <c r="E13" t="n">
-        <v>486.666666666667</v>
-      </c>
-      <c r="F13" t="n">
-        <v>780</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1200</v>
-      </c>
-      <c r="H13" t="n">
-        <v>481.234523560672</v>
-      </c>
-      <c r="I13" t="n">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <sheetPr>
-    <tabColor rgb="FFFF0000"/>
-  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
@@ -2623,75 +2405,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>112</v>
+      <c r="A1" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B4" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B8" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="B9" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
